--- a/architecture/IdentityCertificatesAndAuthentications/ArchitectureDesignAndAuditDocs/FrontEnd_Write_Surface_Audit_v1.xlsx
+++ b/architecture/IdentityCertificatesAndAuthentications/ArchitectureDesignAndAuditDocs/FrontEnd_Write_Surface_Audit_v1.xlsx
@@ -1450,12 +1450,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Library (chathealthy-frontend-lib)</t>
+          <t>Library (chathealthy-lib)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>sharedServices/.../authorizations_and_authentications_tool.py:243, Code/ConversationalUX/FindCareChat/backend/app.py:91 and :301, evaluateCare/Code/healthcheck/health_endpoint.py:63, sharedServices/Code/healthcheck/health_endpoint.py:63, FrontEndApplicationLib/.../logging_service.py:235.</t>
+          <t>sharedServices/.../authorizations_and_authentications_tool.py:243, Code/ConversationalUX/FindCareChat/backend/app.py:91 and :301, evaluateCare/Code/healthcheck/health_endpoint.py:63, sharedServices/Code/healthcheck/health_endpoint.py:63, ChatHealthyLib/.../logging_service.py:235.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
